--- a/docs/manual-tests/workflow_tracker_manual_ui_tests.xlsx
+++ b/docs/manual-tests/workflow_tracker_manual_ui_tests.xlsx
@@ -2,18 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R7c506b53daab4e4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-001 Create Item" sheetId="2" r:id="R27aefe360cde440a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-002 No Title" sheetId="3" r:id="R5aec62f67a6d44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-003 Owner Desc" sheetId="4" r:id="Rd7550e7cae3748b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-004 Happy Path" sheetId="5" r:id="R8fc921b46b174878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-005 Reject NEW-CLOSED" sheetId="6" r:id="R5c73630e004f449f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-006 OPEN Rules" sheetId="7" r:id="R2e3856b67611427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-007 Search" sheetId="8" r:id="R4850cedc78484877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-008 Status Filter" sheetId="9" r:id="R2ac9fe95770f4cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-009 Edit Save" sheetId="10" r:id="Rc2f54d86eb534e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-010 Unsaved Changes" sheetId="11" r:id="R3b76839f816c47b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-011 Status History" sheetId="12" r:id="R4a68251db4214419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R5317d9e2a9354f5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-001 Create Item" sheetId="2" r:id="Rf43b8755a5914d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-002 No Title" sheetId="3" r:id="R84e2dfb1cd6b467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-003 Owner Desc" sheetId="4" r:id="R6855c58b7fae4b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-004 Happy Path" sheetId="5" r:id="R56c6b74712e746e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-005 Reject NEW-CLOSED" sheetId="6" r:id="Rb45f9873b1324797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-006 OPEN Rules" sheetId="7" r:id="Rfe2df554f1eb4c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-007 Search" sheetId="8" r:id="R722fb4d0cf8047a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-008 Status Filter" sheetId="9" r:id="Rb8433af5af4e4835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-009 Edit Save" sheetId="10" r:id="R75cf074fc8b4446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-010 Unsaved Changes" sheetId="11" r:id="Ra7865192df814b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-011 Status History" sheetId="12" r:id="Rc494e4f7bd4644b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-012 Backward Status" sheetId="13" r:id="R303e43cc9945489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-013 Reopen History" sheetId="14" r:id="R598fa57b0b3f404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-014 Unassign Owner" sheetId="15" r:id="R566d6a782e014009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-015 Revert Edits" sheetId="16" r:id="R30b87225cb234110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI-016 Detail Layout" sheetId="17" r:id="Rab1b440e49124d75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -163,108 +168,30 @@
         <x:color rgb="FFD9D9D9"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="38"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="120">
+  <x:cellXfs count="129">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
@@ -569,6 +496,33 @@
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -851,255 +805,363 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="64" t="inlineStr">
+      <x:c r="A1" s="124" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Workflow Tracker — Manual UI Test Suite</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="1" t="n"/>
-      <x:c r="C1" s="1" t="n"/>
-      <x:c r="D1" s="1" t="n"/>
-      <x:c r="E1" s="1" t="n"/>
-      <x:c r="F1" s="1" t="n"/>
+      <x:c r="B1" s="75" t="n"/>
+      <x:c r="C1" s="75" t="n"/>
+      <x:c r="D1" s="75" t="n"/>
+      <x:c r="E1" s="75" t="n"/>
+      <x:c r="F1" s="75" t="n"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="75"/>
+      <x:c r="B2" s="75"/>
+      <x:c r="C2" s="75"/>
+      <x:c r="D2" s="75"/>
+      <x:c r="E2" s="75"/>
+      <x:c r="F2" s="75"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="116" t="str">
+      <x:c r="A3" s="121" t="str">
         <x:v>Test ID</x:v>
       </x:c>
-      <x:c r="B3" s="116" t="str">
+      <x:c r="B3" s="121" t="str">
         <x:v>Test Title</x:v>
       </x:c>
-      <x:c r="C3" s="116" t="str">
+      <x:c r="C3" s="121" t="str">
         <x:v>Automated Equivalent</x:v>
       </x:c>
-      <x:c r="D3" s="116" t="str">
+      <x:c r="D3" s="121" t="str">
         <x:v>Primary Requirement Coverage</x:v>
       </x:c>
-      <x:c r="E3" s="116" t="str">
+      <x:c r="E3" s="121" t="str">
         <x:v>Execution Result</x:v>
       </x:c>
-      <x:c r="F3" s="116" t="str">
+      <x:c r="F3" s="121" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="117" t="str">
+      <x:c r="A4" s="122" t="str">
         <x:v>UI-001</x:v>
       </x:c>
-      <x:c r="B4" s="118" t="str">
+      <x:c r="B4" s="123" t="str">
         <x:v>Create a New Work Item</x:v>
       </x:c>
-      <x:c r="C4" s="118" t="str">
+      <x:c r="C4" s="123" t="str">
         <x:v>CreateWorkItemTest.createsANewItemAndDisplaysItInTheTable()</x:v>
       </x:c>
-      <x:c r="D4" s="118" t="str">
+      <x:c r="D4" s="123" t="str">
         <x:v>WF-001; WF-002; WF-006</x:v>
       </x:c>
-      <x:c r="E4" s="118" t="str">
+      <x:c r="E4" s="123" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F4" s="118" t="str">
-        <x:v>Happy-path creation</x:v>
+      <x:c r="F4" s="123" t="str">
+        <x:v>Creation + explicit post-success form reset</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="117" t="str">
+      <x:c r="A5" s="122" t="str">
         <x:v>UI-002</x:v>
       </x:c>
-      <x:c r="B5" s="118" t="str">
+      <x:c r="B5" s="123" t="str">
         <x:v>Reject Creation with No Title</x:v>
       </x:c>
-      <x:c r="C5" s="118" t="str">
+      <x:c r="C5" s="123" t="str">
         <x:v>CreateWorkItemTest.rejectsAnItemWithNoTitle()</x:v>
       </x:c>
-      <x:c r="D5" s="118" t="str">
+      <x:c r="D5" s="123" t="str">
         <x:v>WF-006</x:v>
       </x:c>
-      <x:c r="E5" s="118" t="str">
+      <x:c r="E5" s="123" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F5" s="118" t="str">
+      <x:c r="F5" s="123" t="str">
         <x:v>Negative title validation</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="119" t="str">
+      <x:c r="A6" s="75" t="str">
         <x:v>UI-003</x:v>
       </x:c>
-      <x:c r="B6" s="119" t="str">
+      <x:c r="B6" s="75" t="str">
         <x:v>Create with Owner and Description</x:v>
       </x:c>
-      <x:c r="C6" s="119" t="str">
+      <x:c r="C6" s="75" t="str">
         <x:v>CreateWorkItemTest.createsAnItemWithOwnerAndDescription()</x:v>
       </x:c>
-      <x:c r="D6" s="119" t="str">
+      <x:c r="D6" s="75" t="str">
         <x:v>WF-001; WF-002; WF-006</x:v>
       </x:c>
-      <x:c r="E6" s="119" t="str">
+      <x:c r="E6" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F6" s="119" t="str">
-        <x:v>Creation field/display check</x:v>
+      <x:c r="F6" s="75" t="str">
+        <x:v>Creation + owner verified in list and Details</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="119" t="str">
+      <x:c r="A7" s="75" t="str">
         <x:v>UI-004</x:v>
       </x:c>
-      <x:c r="B7" s="119" t="str">
+      <x:c r="B7" s="75" t="str">
         <x:v>Normal Status Workflow</x:v>
       </x:c>
-      <x:c r="C7" s="119" t="str">
+      <x:c r="C7" s="75" t="str">
         <x:v>StatusWorkflowTest.movesAnItemThroughTheHappyPathWorkflow()</x:v>
       </x:c>
-      <x:c r="D7" s="119" t="str">
+      <x:c r="D7" s="75" t="str">
         <x:v>WF-002</x:v>
       </x:c>
-      <x:c r="E7" s="119" t="str">
+      <x:c r="E7" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F7" s="119" t="str">
+      <x:c r="F7" s="75" t="str">
         <x:v>NEW → IN_PROGRESS → RESOLVED → CLOSED</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="119" t="str">
+      <x:c r="A8" s="75" t="str">
         <x:v>UI-005</x:v>
       </x:c>
-      <x:c r="B8" s="119" t="str">
+      <x:c r="B8" s="75" t="str">
         <x:v>Reject NEW to CLOSED</x:v>
       </x:c>
-      <x:c r="C8" s="119" t="str">
+      <x:c r="C8" s="75" t="str">
         <x:v>StatusWorkflowTest.rejectsDirectTransitionFromNewToClosed()</x:v>
       </x:c>
-      <x:c r="D8" s="119" t="str">
+      <x:c r="D8" s="75" t="str">
         <x:v>WF-002; WF-003</x:v>
       </x:c>
-      <x:c r="E8" s="119" t="str">
+      <x:c r="E8" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F8" s="119" t="str">
+      <x:c r="F8" s="75" t="str">
         <x:v>Invalid transition</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="119" t="str">
+      <x:c r="A9" s="75" t="str">
         <x:v>UI-006</x:v>
       </x:c>
-      <x:c r="B9" s="119" t="str">
+      <x:c r="B9" s="75" t="str">
         <x:v>Exercise OPEN Status Rules</x:v>
       </x:c>
-      <x:c r="C9" s="119" t="str">
+      <x:c r="C9" s="75" t="str">
         <x:v>StatusWorkflowTest.movesInAndOutOfOpenStatus()</x:v>
       </x:c>
-      <x:c r="D9" s="119" t="str">
+      <x:c r="D9" s="75" t="str">
         <x:v>WF-002</x:v>
       </x:c>
-      <x:c r="E9" s="119" t="str">
+      <x:c r="E9" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F9" s="119" t="str">
+      <x:c r="F9" s="75" t="str">
         <x:v>Allowed and rejected OPEN transitions</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="119" t="str">
+      <x:c r="A10" s="75" t="str">
         <x:v>UI-007</x:v>
       </x:c>
-      <x:c r="B10" s="119" t="str">
+      <x:c r="B10" s="75" t="str">
         <x:v>Search by Title</x:v>
       </x:c>
-      <x:c r="C10" s="119" t="str">
+      <x:c r="C10" s="75" t="str">
         <x:v>SearchAndFilterTest.searchNarrowsTheListByTitle()</x:v>
       </x:c>
-      <x:c r="D10" s="119" t="str">
+      <x:c r="D10" s="75" t="str">
         <x:v>Regression / existing search</x:v>
       </x:c>
-      <x:c r="E10" s="119" t="str">
+      <x:c r="E10" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F10" s="119" t="str">
+      <x:c r="F10" s="75" t="str">
         <x:v>Search regression</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="119" t="str">
+      <x:c r="A11" s="75" t="str">
         <x:v>UI-008</x:v>
       </x:c>
-      <x:c r="B11" s="119" t="str">
+      <x:c r="B11" s="75" t="str">
         <x:v>Filter by Status</x:v>
       </x:c>
-      <x:c r="C11" s="119" t="str">
+      <x:c r="C11" s="75" t="str">
         <x:v>SearchAndFilterTest.filteringByStatusShowsOnlyMatchingItems()</x:v>
       </x:c>
-      <x:c r="D11" s="119" t="str">
+      <x:c r="D11" s="75" t="str">
         <x:v>WF-002 + regression filter</x:v>
       </x:c>
-      <x:c r="E11" s="119" t="str">
+      <x:c r="E11" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F11" s="119" t="str">
+      <x:c r="F11" s="75" t="str">
         <x:v>Automation setup mismatch noted</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="119" t="str">
+      <x:c r="A12" s="75" t="str">
         <x:v>UI-009</x:v>
       </x:c>
-      <x:c r="B12" s="119" t="str">
+      <x:c r="B12" s="75" t="str">
         <x:v>Edit and Save Details</x:v>
       </x:c>
-      <x:c r="C12" s="119" t="str">
+      <x:c r="C12" s="75" t="str">
         <x:v>WorkItemDetailTest.editsAndSavesWorkItemDetails()</x:v>
       </x:c>
-      <x:c r="D12" s="119" t="str">
+      <x:c r="D12" s="75" t="str">
         <x:v>WF-001; WF-004; WF-005</x:v>
       </x:c>
-      <x:c r="E12" s="119" t="str">
+      <x:c r="E12" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F12" s="119" t="str">
-        <x:v>Detail edit/save</x:v>
+      <x:c r="F12" s="75" t="str">
+        <x:v>Detail edit/save + persisted fields/timestamps</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="119" t="str">
+      <x:c r="A13" s="75" t="str">
         <x:v>UI-010</x:v>
       </x:c>
-      <x:c r="B13" s="119" t="str">
+      <x:c r="B13" s="75" t="str">
         <x:v>Protect Unsaved Changes</x:v>
       </x:c>
-      <x:c r="C13" s="119" t="str">
+      <x:c r="C13" s="75" t="str">
         <x:v>WorkItemDetailTest.promptsToDiscardUnsavedChangesOnClose()</x:v>
       </x:c>
-      <x:c r="D13" s="119" t="str">
+      <x:c r="D13" s="75" t="str">
         <x:v>WF-005</x:v>
       </x:c>
-      <x:c r="E13" s="119" t="str">
+      <x:c r="E13" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F13" s="119" t="str">
+      <x:c r="F13" s="75" t="str">
         <x:v>Discard confirmation</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="119" t="str">
+      <x:c r="A14" s="75" t="str">
         <x:v>UI-011</x:v>
       </x:c>
-      <x:c r="B14" s="119" t="str">
+      <x:c r="B14" s="75" t="str">
         <x:v>Verify Status History</x:v>
       </x:c>
-      <x:c r="C14" s="119" t="str">
+      <x:c r="C14" s="75" t="str">
         <x:v>WorkItemDetailTest.showsStatusHistoryForCreationAndTransitions()</x:v>
       </x:c>
-      <x:c r="D14" s="119" t="str">
+      <x:c r="D14" s="75" t="str">
         <x:v>WF-002; WF-003</x:v>
       </x:c>
-      <x:c r="E14" s="119" t="str">
+      <x:c r="E14" s="75" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="F14" s="119" t="str">
+      <x:c r="F14" s="75" t="str">
         <x:v>Creation + transition history</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="75" t="str">
+        <x:v>UI-012</x:v>
+      </x:c>
+      <x:c r="B15" s="75" t="str">
+        <x:v>Allowed Backward Status Transitions</x:v>
+      </x:c>
+      <x:c r="C15" s="75" t="str">
+        <x:v>StatusWorkflowTest.supportsAllAllowedBackwardTransitions()</x:v>
+      </x:c>
+      <x:c r="D15" s="75" t="str">
+        <x:v>WF-002</x:v>
+      </x:c>
+      <x:c r="E15" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="F15" s="75" t="str">
+        <x:v>IN_PROGRESS/RESOLVED backward transitions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="75" t="str">
+        <x:v>UI-013</x:v>
+      </x:c>
+      <x:c r="B16" s="75" t="str">
+        <x:v>Reopen Closed Item + Preserve History</x:v>
+      </x:c>
+      <x:c r="C16" s="75" t="str">
+        <x:v>StatusWorkflowTest.preservesStatusHistoryWhenReopenedFromClosed()</x:v>
+      </x:c>
+      <x:c r="D16" s="75" t="str">
+        <x:v>WF-002; WF-003</x:v>
+      </x:c>
+      <x:c r="E16" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="F16" s="75" t="str">
+        <x:v>CLOSED -&gt; OPEN + history preservation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="75" t="str">
+        <x:v>UI-014</x:v>
+      </x:c>
+      <x:c r="B17" s="75" t="str">
+        <x:v>Change Owner to Unassigned</x:v>
+      </x:c>
+      <x:c r="C17" s="75" t="str">
+        <x:v>WorkItemDetailTest.changesOwnerFromAssignedToUnassigned()</x:v>
+      </x:c>
+      <x:c r="D17" s="75" t="str">
+        <x:v>WF-001; WF-005</x:v>
+      </x:c>
+      <x:c r="E17" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="F17" s="75" t="str">
+        <x:v>Assigned -&gt; Unassigned persists</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="75" t="str">
+        <x:v>UI-015</x:v>
+      </x:c>
+      <x:c r="B18" s="75" t="str">
+        <x:v>Revert Edits Disables Save</x:v>
+      </x:c>
+      <x:c r="C18" s="75" t="str">
+        <x:v>WorkItemDetailTest.revertingEditsToOriginalValuesDisablesSaveChangesAgain()</x:v>
+      </x:c>
+      <x:c r="D18" s="75" t="str">
+        <x:v>WF-005</x:v>
+      </x:c>
+      <x:c r="E18" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="F18" s="75" t="str">
+        <x:v>Dirty state clears after revert</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="75" t="str">
+        <x:v>UI-016</x:v>
+      </x:c>
+      <x:c r="B19" s="75" t="str">
+        <x:v>Detail Edit Controls and Layout</x:v>
+      </x:c>
+      <x:c r="C19" s="75" t="str">
+        <x:v>Manual only — visual/layout verification</x:v>
+      </x:c>
+      <x:c r="D19" s="75" t="str">
+        <x:v>WF-005</x:v>
+      </x:c>
+      <x:c r="E19" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="F19" s="75" t="str">
+        <x:v>Single Save action + fixed Description + bottom-right action layout</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1107,8 +1169,8 @@
     <x:mergeCell ref="A1:F1"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="Re059e255f29141ea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="R6d70f21c8e754a2a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="R8b857a1ebbd34470"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="R511d507c2ed443e2"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1286,14 +1348,14 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B15" s="109" t="str">
-        <x:v>Observe the detail view and work-item list.</x:v>
+        <x:v>Observe the work-item list after saving.</x:v>
       </x:c>
       <x:c r="C15" s="109" t="str">
-        <x:v>Detail view closes; the list shows the new title and owner.</x:v>
+        <x:v>Detail view closes; the list shows the new title and owner, and the Updated value reflects the save.</x:v>
       </x:c>
       <x:c r="D15" s="109" t="str"/>
       <x:c r="E15" s="110" t="str">
-        <x:v>WF-005 AC-6; WF-001 AC-3</x:v>
+        <x:v>WF-005 AC-6; WF-001 AC-3; WF-001 AC-8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="66" hidden="0" customHeight="1">
@@ -1301,14 +1363,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B16" s="109" t="str">
-        <x:v>Reopen Details for the renamed item.</x:v>
+        <x:v>Reopen Details for the renamed item and inspect all saved fields.</x:v>
       </x:c>
       <x:c r="C16" s="109" t="str">
-        <x:v>The updated description is displayed.</x:v>
+        <x:v>The new title, owner, and description are displayed, and the detail Updated timestamp reflects the saved edit.</x:v>
       </x:c>
       <x:c r="D16" s="109" t="str"/>
       <x:c r="E16" s="110" t="str">
-        <x:v>WF-004 AC-1; WF-004 AC-2</x:v>
+        <x:v>WF-001 AC-4; WF-004 AC-1; WF-004 AC-2; WF-004 AC-3; WF-005 AC-6</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -1316,10 +1378,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="112" t="str">
-        <x:v>If modification time is visible, compare it with the original.</x:v>
+        <x:v>Compare the displayed modification time with the original value.</x:v>
       </x:c>
       <x:c r="C17" s="112" t="str">
-        <x:v>Modification timestamp reflects the saved edit.</x:v>
+        <x:v>Modification timestamp changed as a result of the saved edit.</x:v>
       </x:c>
       <x:c r="D17" s="112" t="str"/>
       <x:c r="E17" s="113" t="str">
@@ -1950,6 +2012,1345 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="75" t="str">
+        <x:v>UI-012 — Exercise Allowed Backward Status Transitions</x:v>
+      </x:c>
+      <x:c r="B1" s="75"/>
+      <x:c r="C1" s="75"/>
+      <x:c r="D1" s="75"/>
+      <x:c r="E1" s="75"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="75"/>
+      <x:c r="B2" s="75"/>
+      <x:c r="C2" s="75"/>
+      <x:c r="D2" s="75"/>
+      <x:c r="E2" s="75"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="75" t="str">
+        <x:v>Automated Equivalent</x:v>
+      </x:c>
+      <x:c r="B3" s="75" t="str">
+        <x:v>StatusWorkflowTest.supportsAllAllowedBackwardTransitions()</x:v>
+      </x:c>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Verify the documented backward status transitions that return work to an earlier workflow state.</x:v>
+      </x:c>
+      <x:c r="C4" s="75"/>
+      <x:c r="D4" s="75"/>
+      <x:c r="E4" s="75"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="75" t="str">
+        <x:v>Preconditions</x:v>
+      </x:c>
+      <x:c r="B5" s="75" t="str">
+        <x:v>Workflow Tracker is running and accessible. The test environment is available for manual execution.</x:v>
+      </x:c>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="75" t="str">
+        <x:v>Test Data</x:v>
+      </x:c>
+      <x:c r="B6" s="75" t="str">
+        <x:v>Create uniquely titled items as needed to exercise:
+IN_PROGRESS -&gt; OPEN
+RESOLVED -&gt; IN_PROGRESS
+RESOLVED -&gt; OPEN</x:v>
+      </x:c>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="75"/>
+      <x:c r="E6" s="75"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="75" t="str">
+        <x:v>Assumptions</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="str">
+        <x:v>Each item can be moved through the valid forward path needed to reach the starting status for the backward transition.</x:v>
+      </x:c>
+      <x:c r="C7" s="75"/>
+      <x:c r="D7" s="75"/>
+      <x:c r="E7" s="75"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="75" t="str">
+        <x:v>Tools Needed</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="str">
+        <x:v>Supported web browser; Workflow Tracker application URL.</x:v>
+      </x:c>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="75"/>
+      <x:c r="B9" s="75"/>
+      <x:c r="C9" s="75"/>
+      <x:c r="D9" s="75"/>
+      <x:c r="E9" s="75"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="75" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B10" s="75" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="C10" s="75" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+      <x:c r="D10" s="75" t="str">
+        <x:v>Actual Result</x:v>
+      </x:c>
+      <x:c r="E10" s="75" t="str">
+        <x:v>Requirement(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B11" s="75" t="str">
+        <x:v>Create an item and move it NEW -&gt; IN_PROGRESS.</x:v>
+      </x:c>
+      <x:c r="C11" s="75" t="str">
+        <x:v>Item reaches IN PROGRESS.</x:v>
+      </x:c>
+      <x:c r="D11" s="75"/>
+      <x:c r="E11" s="75" t="str">
+        <x:v>WF-002 AC-4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="75" t="str">
+        <x:v>Change status from IN_PROGRESS to OPEN.</x:v>
+      </x:c>
+      <x:c r="C12" s="75" t="str">
+        <x:v>Status changes to OPEN.</x:v>
+      </x:c>
+      <x:c r="D12" s="75"/>
+      <x:c r="E12" s="75" t="str">
+        <x:v>WF-002 AC-8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="75" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>Create or reset an item through NEW -&gt; IN_PROGRESS -&gt; RESOLVED.</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="str">
+        <x:v>Item reaches RESOLVED.</x:v>
+      </x:c>
+      <x:c r="D13" s="75"/>
+      <x:c r="E13" s="75" t="str">
+        <x:v>WF-002 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="75" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="75" t="str">
+        <x:v>Change status from RESOLVED to IN_PROGRESS.</x:v>
+      </x:c>
+      <x:c r="C14" s="75" t="str">
+        <x:v>Status changes to IN PROGRESS.</x:v>
+      </x:c>
+      <x:c r="D14" s="75"/>
+      <x:c r="E14" s="75" t="str">
+        <x:v>WF-002 AC-9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="75" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B15" s="75" t="str">
+        <x:v>Return an item to RESOLVED using the valid workflow.</x:v>
+      </x:c>
+      <x:c r="C15" s="75" t="str">
+        <x:v>Item reaches RESOLVED again.</x:v>
+      </x:c>
+      <x:c r="D15" s="75"/>
+      <x:c r="E15" s="75" t="str">
+        <x:v>WF-002 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="75" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B16" s="75" t="str">
+        <x:v>Change status from RESOLVED to OPEN.</x:v>
+      </x:c>
+      <x:c r="C16" s="75" t="str">
+        <x:v>Status changes to OPEN.</x:v>
+      </x:c>
+      <x:c r="D16" s="75"/>
+      <x:c r="E16" s="75" t="str">
+        <x:v>WF-002 AC-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="75"/>
+      <x:c r="B17" s="75"/>
+      <x:c r="C17" s="75"/>
+      <x:c r="D17" s="75"/>
+      <x:c r="E17" s="75"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="75" t="str">
+        <x:v>Manual Observations / Execution Notes</x:v>
+      </x:c>
+      <x:c r="B18" s="75"/>
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="75" t="str">
+        <x:v>Record any unexpected restrictions, stale status display, timing issues, or behavior that differs depending on the route used to reach the starting status.</x:v>
+      </x:c>
+      <x:c r="B19" s="75"/>
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="75"/>
+      <x:c r="B20" s="75"/>
+      <x:c r="C20" s="75"/>
+      <x:c r="D20" s="75"/>
+      <x:c r="E20" s="75"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="75"/>
+      <x:c r="B21" s="75"/>
+      <x:c r="C21" s="75"/>
+      <x:c r="D21" s="75"/>
+      <x:c r="E21" s="75"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="75"/>
+      <x:c r="B22" s="75"/>
+      <x:c r="C22" s="75"/>
+      <x:c r="D22" s="75"/>
+      <x:c r="E22" s="75"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="75"/>
+      <x:c r="B23" s="75"/>
+      <x:c r="C23" s="75"/>
+      <x:c r="D23" s="75"/>
+      <x:c r="E23" s="75"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="75" t="str">
+        <x:v>Execution Result</x:v>
+      </x:c>
+      <x:c r="B24" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="C24" s="75" t="str">
+        <x:v>Executed By</x:v>
+      </x:c>
+      <x:c r="D24" s="75"/>
+      <x:c r="E24" s="75"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="75" t="str">
+        <x:v>UI-013 — Reopen a Closed Item and Preserve Status History</x:v>
+      </x:c>
+      <x:c r="B1" s="75"/>
+      <x:c r="C1" s="75"/>
+      <x:c r="D1" s="75"/>
+      <x:c r="E1" s="75"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="75"/>
+      <x:c r="B2" s="75"/>
+      <x:c r="C2" s="75"/>
+      <x:c r="D2" s="75"/>
+      <x:c r="E2" s="75"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="75" t="str">
+        <x:v>Automated Equivalent</x:v>
+      </x:c>
+      <x:c r="B3" s="75" t="str">
+        <x:v>StatusWorkflowTest.preservesStatusHistoryWhenReopenedFromClosed()</x:v>
+      </x:c>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Verify that CLOSED can reopen to OPEN and that the item's complete status history remains intact after reopening.</x:v>
+      </x:c>
+      <x:c r="C4" s="75"/>
+      <x:c r="D4" s="75"/>
+      <x:c r="E4" s="75"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="75" t="str">
+        <x:v>Preconditions</x:v>
+      </x:c>
+      <x:c r="B5" s="75" t="str">
+        <x:v>Workflow Tracker is running and accessible. The test environment is available for manual execution.</x:v>
+      </x:c>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="75" t="str">
+        <x:v>Test Data</x:v>
+      </x:c>
+      <x:c r="B6" s="75" t="str">
+        <x:v>Title: Manual test - reopen history &lt;unique value&gt;
+Owner: Unassigned
+Path: NEW -&gt; IN_PROGRESS -&gt; RESOLVED -&gt; CLOSED -&gt; OPEN</x:v>
+      </x:c>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="75"/>
+      <x:c r="E6" s="75"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="75" t="str">
+        <x:v>Assumptions</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="str">
+        <x:v>The Details view exposes chronological status history for the created item.</x:v>
+      </x:c>
+      <x:c r="C7" s="75"/>
+      <x:c r="D7" s="75"/>
+      <x:c r="E7" s="75"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="75" t="str">
+        <x:v>Tools Needed</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="str">
+        <x:v>Supported web browser; Workflow Tracker application URL.</x:v>
+      </x:c>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="75"/>
+      <x:c r="B9" s="75"/>
+      <x:c r="C9" s="75"/>
+      <x:c r="D9" s="75"/>
+      <x:c r="E9" s="75"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="75" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B10" s="75" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="C10" s="75" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+      <x:c r="D10" s="75" t="str">
+        <x:v>Actual Result</x:v>
+      </x:c>
+      <x:c r="E10" s="75" t="str">
+        <x:v>Requirement(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B11" s="75" t="str">
+        <x:v>Create a new work item.</x:v>
+      </x:c>
+      <x:c r="C11" s="75" t="str">
+        <x:v>Item appears with status NEW and an initial history entry is created.</x:v>
+      </x:c>
+      <x:c r="D11" s="75"/>
+      <x:c r="E11" s="75" t="str">
+        <x:v>WF-002 AC-2; WF-003 AC-2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="75" t="str">
+        <x:v>Move the item NEW -&gt; IN_PROGRESS -&gt; RESOLVED -&gt; CLOSED.</x:v>
+      </x:c>
+      <x:c r="C12" s="75" t="str">
+        <x:v>Each valid transition succeeds and the item reaches CLOSED.</x:v>
+      </x:c>
+      <x:c r="D12" s="75"/>
+      <x:c r="E12" s="75" t="str">
+        <x:v>WF-002 AC-4; WF-002 AC-6; WF-002 AC-7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="75" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>Open Details and inspect Status History before reopening.</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="str">
+        <x:v>History contains the creation entry plus the three completed transitions.</x:v>
+      </x:c>
+      <x:c r="D13" s="75"/>
+      <x:c r="E13" s="75" t="str">
+        <x:v>WF-003 AC-1; WF-003 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="75" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="75" t="str">
+        <x:v>Close Details and change status from CLOSED to OPEN.</x:v>
+      </x:c>
+      <x:c r="C14" s="75" t="str">
+        <x:v>Status changes to OPEN.</x:v>
+      </x:c>
+      <x:c r="D14" s="75"/>
+      <x:c r="E14" s="75" t="str">
+        <x:v>WF-002 AC-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="75" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B15" s="75" t="str">
+        <x:v>Reopen Details and inspect Status History.</x:v>
+      </x:c>
+      <x:c r="C15" s="75" t="str">
+        <x:v>The prior history is preserved and a CLOSED -&gt; OPEN entry is appended; no earlier entries are lost.</x:v>
+      </x:c>
+      <x:c r="D15" s="75"/>
+      <x:c r="E15" s="75" t="str">
+        <x:v>WF-003 AC-5; WF-003 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="75" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B16" s="75" t="str">
+        <x:v>Review the full history sequence and timestamps.</x:v>
+      </x:c>
+      <x:c r="C16" s="75" t="str">
+        <x:v>Entries remain associated with this item, ordered correctly, and show plausible timestamps.</x:v>
+      </x:c>
+      <x:c r="D16" s="75"/>
+      <x:c r="E16" s="75" t="str">
+        <x:v>WF-003 AC-2; WF-003 AC-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="75"/>
+      <x:c r="B17" s="75"/>
+      <x:c r="C17" s="75"/>
+      <x:c r="D17" s="75"/>
+      <x:c r="E17" s="75"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="75" t="str">
+        <x:v>Manual Observations / Execution Notes</x:v>
+      </x:c>
+      <x:c r="B18" s="75"/>
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="75" t="str">
+        <x:v>Watch for missing, duplicated, reordered, or replaced history rows after reopening. Confirm reopening adds to history rather than resetting it.</x:v>
+      </x:c>
+      <x:c r="B19" s="75"/>
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="75"/>
+      <x:c r="B20" s="75"/>
+      <x:c r="C20" s="75"/>
+      <x:c r="D20" s="75"/>
+      <x:c r="E20" s="75"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="75"/>
+      <x:c r="B21" s="75"/>
+      <x:c r="C21" s="75"/>
+      <x:c r="D21" s="75"/>
+      <x:c r="E21" s="75"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="75"/>
+      <x:c r="B22" s="75"/>
+      <x:c r="C22" s="75"/>
+      <x:c r="D22" s="75"/>
+      <x:c r="E22" s="75"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="75"/>
+      <x:c r="B23" s="75"/>
+      <x:c r="C23" s="75"/>
+      <x:c r="D23" s="75"/>
+      <x:c r="E23" s="75"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="75" t="str">
+        <x:v>Execution Result</x:v>
+      </x:c>
+      <x:c r="B24" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="C24" s="75" t="str">
+        <x:v>Executed By</x:v>
+      </x:c>
+      <x:c r="D24" s="75"/>
+      <x:c r="E24" s="75"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="75" t="str">
+        <x:v>UI-014 — Change an Assigned Owner to Unassigned</x:v>
+      </x:c>
+      <x:c r="B1" s="75"/>
+      <x:c r="C1" s="75"/>
+      <x:c r="D1" s="75"/>
+      <x:c r="E1" s="75"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="75"/>
+      <x:c r="B2" s="75"/>
+      <x:c r="C2" s="75"/>
+      <x:c r="D2" s="75"/>
+      <x:c r="E2" s="75"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="75" t="str">
+        <x:v>Automated Equivalent</x:v>
+      </x:c>
+      <x:c r="B3" s="75" t="str">
+        <x:v>WorkItemDetailTest.changesOwnerFromAssignedToUnassigned()</x:v>
+      </x:c>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Verify that an assigned work item can be changed to Unassigned and that the change persists in both list and detail views.</x:v>
+      </x:c>
+      <x:c r="C4" s="75"/>
+      <x:c r="D4" s="75"/>
+      <x:c r="E4" s="75"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="75" t="str">
+        <x:v>Preconditions</x:v>
+      </x:c>
+      <x:c r="B5" s="75" t="str">
+        <x:v>Workflow Tracker is running and accessible. The test environment is available for manual execution.</x:v>
+      </x:c>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="75" t="str">
+        <x:v>Test Data</x:v>
+      </x:c>
+      <x:c r="B6" s="75" t="str">
+        <x:v>Title: Manual test - unassign owner &lt;unique value&gt;
+Initial owner: FirstName1 LastName1
+Description: Owner will be removed</x:v>
+      </x:c>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="75"/>
+      <x:c r="E6" s="75"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="75" t="str">
+        <x:v>Assumptions</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="str">
+        <x:v>FirstName1 LastName1 exists as a selectable owner and the Details view allows Owner to be changed to Unassigned.</x:v>
+      </x:c>
+      <x:c r="C7" s="75"/>
+      <x:c r="D7" s="75"/>
+      <x:c r="E7" s="75"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="75" t="str">
+        <x:v>Tools Needed</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="str">
+        <x:v>Supported web browser; Workflow Tracker application URL.</x:v>
+      </x:c>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="75"/>
+      <x:c r="B9" s="75"/>
+      <x:c r="C9" s="75"/>
+      <x:c r="D9" s="75"/>
+      <x:c r="E9" s="75"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="75" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B10" s="75" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="C10" s="75" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+      <x:c r="D10" s="75" t="str">
+        <x:v>Actual Result</x:v>
+      </x:c>
+      <x:c r="E10" s="75" t="str">
+        <x:v>Requirement(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B11" s="75" t="str">
+        <x:v>Create a work item assigned to FirstName1 LastName1.</x:v>
+      </x:c>
+      <x:c r="C11" s="75" t="str">
+        <x:v>The new item displays FirstName1 LastName1 as Owner.</x:v>
+      </x:c>
+      <x:c r="D11" s="75"/>
+      <x:c r="E11" s="75" t="str">
+        <x:v>WF-001 AC-1; WF-001 AC-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="75" t="str">
+        <x:v>Open Details.</x:v>
+      </x:c>
+      <x:c r="C12" s="75" t="str">
+        <x:v>Detail Owner shows FirstName1 LastName1.</x:v>
+      </x:c>
+      <x:c r="D12" s="75"/>
+      <x:c r="E12" s="75" t="str">
+        <x:v>WF-001 AC-4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="75" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>Change Owner to Unassigned.</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="str">
+        <x:v>Save Changes becomes enabled.</x:v>
+      </x:c>
+      <x:c r="D13" s="75"/>
+      <x:c r="E13" s="75" t="str">
+        <x:v>WF-001 AC-6; WF-005 AC-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="75" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="75" t="str">
+        <x:v>Click Save Changes.</x:v>
+      </x:c>
+      <x:c r="C14" s="75" t="str">
+        <x:v>The change is saved and the detail view closes.</x:v>
+      </x:c>
+      <x:c r="D14" s="75"/>
+      <x:c r="E14" s="75" t="str">
+        <x:v>WF-005 AC-5; WF-005 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="75" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B15" s="75" t="str">
+        <x:v>Inspect the work-item list.</x:v>
+      </x:c>
+      <x:c r="C15" s="75" t="str">
+        <x:v>Owner displays Unassigned for the item.</x:v>
+      </x:c>
+      <x:c r="D15" s="75"/>
+      <x:c r="E15" s="75" t="str">
+        <x:v>WF-001 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="75" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B16" s="75" t="str">
+        <x:v>Reopen Details and inspect Owner.</x:v>
+      </x:c>
+      <x:c r="C16" s="75" t="str">
+        <x:v>Owner still displays Unassigned.</x:v>
+      </x:c>
+      <x:c r="D16" s="75"/>
+      <x:c r="E16" s="75" t="str">
+        <x:v>WF-001 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="75"/>
+      <x:c r="B17" s="75"/>
+      <x:c r="C17" s="75"/>
+      <x:c r="D17" s="75"/>
+      <x:c r="E17" s="75"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="75" t="str">
+        <x:v>Manual Observations / Execution Notes</x:v>
+      </x:c>
+      <x:c r="B18" s="75"/>
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="75" t="str">
+        <x:v>Record any stale owner value, inability to select Unassigned, partial-save behavior, or inconsistency between list and detail views.</x:v>
+      </x:c>
+      <x:c r="B19" s="75"/>
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="75"/>
+      <x:c r="B20" s="75"/>
+      <x:c r="C20" s="75"/>
+      <x:c r="D20" s="75"/>
+      <x:c r="E20" s="75"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="75"/>
+      <x:c r="B21" s="75"/>
+      <x:c r="C21" s="75"/>
+      <x:c r="D21" s="75"/>
+      <x:c r="E21" s="75"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="75"/>
+      <x:c r="B22" s="75"/>
+      <x:c r="C22" s="75"/>
+      <x:c r="D22" s="75"/>
+      <x:c r="E22" s="75"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="75"/>
+      <x:c r="B23" s="75"/>
+      <x:c r="C23" s="75"/>
+      <x:c r="D23" s="75"/>
+      <x:c r="E23" s="75"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="75" t="str">
+        <x:v>Execution Result</x:v>
+      </x:c>
+      <x:c r="B24" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="C24" s="75" t="str">
+        <x:v>Executed By</x:v>
+      </x:c>
+      <x:c r="D24" s="75"/>
+      <x:c r="E24" s="75"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="75" t="str">
+        <x:v>UI-015 — Revert Detail Edits and Disable Save Changes</x:v>
+      </x:c>
+      <x:c r="B1" s="75"/>
+      <x:c r="C1" s="75"/>
+      <x:c r="D1" s="75"/>
+      <x:c r="E1" s="75"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="75"/>
+      <x:c r="B2" s="75"/>
+      <x:c r="C2" s="75"/>
+      <x:c r="D2" s="75"/>
+      <x:c r="E2" s="75"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="75" t="str">
+        <x:v>Automated Equivalent</x:v>
+      </x:c>
+      <x:c r="B3" s="75" t="str">
+        <x:v>WorkItemDetailTest.revertingEditsToOriginalValuesDisablesSaveChangesAgain()</x:v>
+      </x:c>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Verify that Save Changes is enabled only while the detail form differs from the saved values and disables again after edits are fully reverted.</x:v>
+      </x:c>
+      <x:c r="C4" s="75"/>
+      <x:c r="D4" s="75"/>
+      <x:c r="E4" s="75"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="75" t="str">
+        <x:v>Preconditions</x:v>
+      </x:c>
+      <x:c r="B5" s="75" t="str">
+        <x:v>Workflow Tracker is running and accessible. The test environment is available for manual execution.</x:v>
+      </x:c>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="75" t="str">
+        <x:v>Test Data</x:v>
+      </x:c>
+      <x:c r="B6" s="75" t="str">
+        <x:v>Title: Manual test - revert edits &lt;unique value&gt;
+Description: Original description</x:v>
+      </x:c>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="75"/>
+      <x:c r="E6" s="75"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="75" t="str">
+        <x:v>Assumptions</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="str">
+        <x:v>The Details view opens with Save Changes disabled and detects dirty/clean form state.</x:v>
+      </x:c>
+      <x:c r="C7" s="75"/>
+      <x:c r="D7" s="75"/>
+      <x:c r="E7" s="75"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="75" t="str">
+        <x:v>Tools Needed</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="str">
+        <x:v>Supported web browser; Workflow Tracker application URL.</x:v>
+      </x:c>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="75"/>
+      <x:c r="B9" s="75"/>
+      <x:c r="C9" s="75"/>
+      <x:c r="D9" s="75"/>
+      <x:c r="E9" s="75"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="75" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B10" s="75" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="C10" s="75" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+      <x:c r="D10" s="75" t="str">
+        <x:v>Actual Result</x:v>
+      </x:c>
+      <x:c r="E10" s="75" t="str">
+        <x:v>Requirement(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B11" s="75" t="str">
+        <x:v>Create an item and open Details.</x:v>
+      </x:c>
+      <x:c r="C11" s="75" t="str">
+        <x:v>Saved values are displayed and Save Changes is disabled.</x:v>
+      </x:c>
+      <x:c r="D11" s="75"/>
+      <x:c r="E11" s="75" t="str">
+        <x:v>WF-005 AC-2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="75" t="str">
+        <x:v>Change the title to a different value.</x:v>
+      </x:c>
+      <x:c r="C12" s="75" t="str">
+        <x:v>Save Changes becomes enabled.</x:v>
+      </x:c>
+      <x:c r="D12" s="75"/>
+      <x:c r="E12" s="75" t="str">
+        <x:v>WF-005 AC-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="75" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>Restore the title exactly to its original saved value.</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="str">
+        <x:v>Save Changes becomes disabled again.</x:v>
+      </x:c>
+      <x:c r="D13" s="75"/>
+      <x:c r="E13" s="75" t="str">
+        <x:v>WF-005 AC-4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="75" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="75" t="str">
+        <x:v>Optionally repeat with Description or Owner and then restore the original value.</x:v>
+      </x:c>
+      <x:c r="C14" s="75" t="str">
+        <x:v>Save Changes follows the same dirty/clean behavior.</x:v>
+      </x:c>
+      <x:c r="D14" s="75"/>
+      <x:c r="E14" s="75" t="str">
+        <x:v>WF-005 AC-4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="75"/>
+      <x:c r="B15" s="75"/>
+      <x:c r="C15" s="75"/>
+      <x:c r="D15" s="75"/>
+      <x:c r="E15" s="75"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="75" t="str">
+        <x:v>Manual Observations / Execution Notes</x:v>
+      </x:c>
+      <x:c r="B16" s="75"/>
+      <x:c r="C16" s="75"/>
+      <x:c r="D16" s="75"/>
+      <x:c r="E16" s="75"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="75" t="str">
+        <x:v>Note whether whitespace, field focus, or reverting multiple fields affects the dirty-state calculation. Record any case where Save remains enabled after all values match the saved state.</x:v>
+      </x:c>
+      <x:c r="B17" s="75"/>
+      <x:c r="C17" s="75"/>
+      <x:c r="D17" s="75"/>
+      <x:c r="E17" s="75"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="75"/>
+      <x:c r="B18" s="75"/>
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="75"/>
+      <x:c r="B19" s="75"/>
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="75"/>
+      <x:c r="B20" s="75"/>
+      <x:c r="C20" s="75"/>
+      <x:c r="D20" s="75"/>
+      <x:c r="E20" s="75"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="75"/>
+      <x:c r="B21" s="75"/>
+      <x:c r="C21" s="75"/>
+      <x:c r="D21" s="75"/>
+      <x:c r="E21" s="75"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="75"/>
+      <x:c r="B22" s="75"/>
+      <x:c r="C22" s="75"/>
+      <x:c r="D22" s="75"/>
+      <x:c r="E22" s="75"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="75"/>
+      <x:c r="B23" s="75"/>
+      <x:c r="C23" s="75"/>
+      <x:c r="D23" s="75"/>
+      <x:c r="E23" s="75"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="75" t="str">
+        <x:v>Execution Result</x:v>
+      </x:c>
+      <x:c r="B24" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="C24" s="75" t="str">
+        <x:v>Executed By</x:v>
+      </x:c>
+      <x:c r="D24" s="75"/>
+      <x:c r="E24" s="75"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="75" t="str">
+        <x:v>UI-016 — Verify Detail Edit Controls and Layout</x:v>
+      </x:c>
+      <x:c r="B1" s="75"/>
+      <x:c r="C1" s="75"/>
+      <x:c r="D1" s="75"/>
+      <x:c r="E1" s="75"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="75"/>
+      <x:c r="B2" s="75"/>
+      <x:c r="C2" s="75"/>
+      <x:c r="D2" s="75"/>
+      <x:c r="E2" s="75"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="75" t="str">
+        <x:v>Automated Equivalent</x:v>
+      </x:c>
+      <x:c r="B3" s="75" t="str">
+        <x:v>Manual only — visual/layout verification</x:v>
+      </x:c>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Verify the detail editor exposes one Save Changes action for all editable fields and follows the specified description/control layout conventions.</x:v>
+      </x:c>
+      <x:c r="C4" s="75"/>
+      <x:c r="D4" s="75"/>
+      <x:c r="E4" s="75"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="75" t="str">
+        <x:v>Preconditions</x:v>
+      </x:c>
+      <x:c r="B5" s="75" t="str">
+        <x:v>Workflow Tracker is running and accessible. At least one work item is available to open in Details.</x:v>
+      </x:c>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="75" t="str">
+        <x:v>Test Data</x:v>
+      </x:c>
+      <x:c r="B6" s="75" t="str">
+        <x:v>Any existing work item with title, owner, and description values.</x:v>
+      </x:c>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="75"/>
+      <x:c r="E6" s="75"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="75" t="str">
+        <x:v>Assumptions</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="str">
+        <x:v>The Details view exposes editable Title, Owner, and Description fields plus Close and Save Changes controls.</x:v>
+      </x:c>
+      <x:c r="C7" s="75"/>
+      <x:c r="D7" s="75"/>
+      <x:c r="E7" s="75"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="75" t="str">
+        <x:v>Tools Needed</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="str">
+        <x:v>Supported web browser; Workflow Tracker application URL.</x:v>
+      </x:c>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="75"/>
+      <x:c r="B9" s="75"/>
+      <x:c r="C9" s="75"/>
+      <x:c r="D9" s="75"/>
+      <x:c r="E9" s="75"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="75" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B10" s="75" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="C10" s="75" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+      <x:c r="D10" s="75" t="str">
+        <x:v>Actual Result</x:v>
+      </x:c>
+      <x:c r="E10" s="75" t="str">
+        <x:v>Requirement(s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B11" s="75" t="str">
+        <x:v>Open Details for an existing work item.</x:v>
+      </x:c>
+      <x:c r="C11" s="75" t="str">
+        <x:v>The editable Title, Owner, and Description fields are visible.</x:v>
+      </x:c>
+      <x:c r="D11" s="75"/>
+      <x:c r="E11" s="75" t="str">
+        <x:v>Setup / not coverage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="75" t="str">
+        <x:v>Inspect the available save controls for the editable fields.</x:v>
+      </x:c>
+      <x:c r="C12" s="75" t="str">
+        <x:v>Exactly one Save Changes button is provided and it applies to the editable detail fields together.</x:v>
+      </x:c>
+      <x:c r="D12" s="75"/>
+      <x:c r="E12" s="75" t="str">
+        <x:v>WF-005 AC-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="75" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>Inspect the Description field and attempt to resize it using normal browser UI affordances.</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="str">
+        <x:v>The Description field has a fixed size and is not user-resizable.</x:v>
+      </x:c>
+      <x:c r="D13" s="75"/>
+      <x:c r="E13" s="75" t="str">
+        <x:v>WF-005 AC-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="75" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="75" t="str">
+        <x:v>Inspect the placement of Close and Save Changes.</x:v>
+      </x:c>
+      <x:c r="C14" s="75" t="str">
+        <x:v>Close and Save Changes are grouped at the bottom-right of the detail view.</x:v>
+      </x:c>
+      <x:c r="D14" s="75"/>
+      <x:c r="E14" s="75" t="str">
+        <x:v>WF-005 AC-13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="75" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B15" s="75" t="str">
+        <x:v>Compare the visual emphasis of the two actions.</x:v>
+      </x:c>
+      <x:c r="C15" s="75" t="str">
+        <x:v>Save Changes is presented as the primary action relative to Close.</x:v>
+      </x:c>
+      <x:c r="D15" s="75"/>
+      <x:c r="E15" s="75" t="str">
+        <x:v>WF-005 AC-13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="75"/>
+      <x:c r="B16" s="75"/>
+      <x:c r="C16" s="75"/>
+      <x:c r="D16" s="75"/>
+      <x:c r="E16" s="75"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="75" t="str">
+        <x:v>Manual Observations / Execution Notes</x:v>
+      </x:c>
+      <x:c r="B17" s="75"/>
+      <x:c r="C17" s="75"/>
+      <x:c r="D17" s="75"/>
+      <x:c r="E17" s="75"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="75" t="str">
+        <x:v>Record browser/zoom level and any visual inconsistency. These checks are intentionally manual because they concern layout, resizing behavior, and visual hierarchy rather than business logic.</x:v>
+      </x:c>
+      <x:c r="B18" s="75"/>
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="75"/>
+      <x:c r="B19" s="75"/>
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="75"/>
+      <x:c r="B20" s="75"/>
+      <x:c r="C20" s="75"/>
+      <x:c r="D20" s="75"/>
+      <x:c r="E20" s="75"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="75"/>
+      <x:c r="B21" s="75"/>
+      <x:c r="C21" s="75"/>
+      <x:c r="D21" s="75"/>
+      <x:c r="E21" s="75"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="75"/>
+      <x:c r="B22" s="75"/>
+      <x:c r="C22" s="75"/>
+      <x:c r="D22" s="75"/>
+      <x:c r="E22" s="75"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="75"/>
+      <x:c r="B23" s="75"/>
+      <x:c r="C23" s="75"/>
+      <x:c r="D23" s="75"/>
+      <x:c r="E23" s="75"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="75" t="str">
+        <x:v>Execution Result</x:v>
+      </x:c>
+      <x:c r="B24" s="75" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="C24" s="75" t="str">
+        <x:v>Executed By</x:v>
+      </x:c>
+      <x:c r="D24" s="75"/>
+      <x:c r="E24" s="75"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2224,21 +3625,15 @@
       <x:c r="A18" s="52" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B18" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Inspect the create form after successful creation.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The form is reset and Create is disabled again.</x:t>
-        </x:is>
+      <x:c r="B18" s="53" t="str">
+        <x:v>Inspect the create form after successful creation.</x:v>
+      </x:c>
+      <x:c r="C18" s="53" t="str">
+        <x:v>Title and Description are blank, Owner is reset to Unassigned, and Create is disabled again.</x:v>
       </x:c>
       <x:c r="D18" s="53" t="str"/>
-      <x:c r="E18" s="54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WF-006 AC-8</x:t>
-        </x:is>
+      <x:c r="E18" s="54" t="str">
+        <x:v>WF-006 AC-8</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2907,6 +4302,21 @@
       <x:c r="D16" s="112" t="str"/>
       <x:c r="E16" s="113" t="str">
         <x:v>WF-002 AC-2; WF-006 AC-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Open Details for the created item and inspect Owner.</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Owner displays FirstName1 LastName1 in the detail view.</x:v>
+      </x:c>
+      <x:c r="D17"/>
+      <x:c r="E17" t="str">
+        <x:v>WF-001 AC-4</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
